--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512473_ELIMINGRD14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512473_ELIMINGRD14FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7539</v>
+        <v>6.6864</v>
       </c>
       <c r="E2" t="n">
-        <v>6.022</v>
+        <v>6.0266</v>
       </c>
       <c r="F2" t="n">
-        <v>0.732</v>
+        <v>0.6599</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9822</v>
+        <v>3.0061</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7615</v>
+        <v>3.8364</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5845</v>
+        <v>3.7639</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4626</v>
+        <v>3.6178</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1219</v>
+        <v>0.146</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.7577</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2989</v>
+        <v>0.2185</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9012</v>
+        <v>-0.9762</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0518</v>
+        <v>0.9529</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7181</v>
+        <v>0.4827</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3337</v>
+        <v>0.4702</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5414</v>
+        <v>4.9843</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7875</v>
+        <v>4.3642</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7539</v>
+        <v>0.62</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4302</v>
+        <v>0.2255</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6391</v>
+        <v>1.0361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7911</v>
+        <v>-0.8105</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7448</v>
+        <v>2.1188</v>
       </c>
       <c r="K3" t="n">
-        <v>1.425</v>
+        <v>1.4215</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3198</v>
+        <v>0.6973</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3146</v>
+        <v>-1.8933</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7859</v>
+        <v>-0.3855</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-1.5078</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6005</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6005</v>
+        <v>2.5316</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5107</v>
+        <v>0.2319</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7829</v>
+        <v>0.2501</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7279</v>
+        <v>-0.0182</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3.9426</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2598</v>
+        <v>3.9426</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0447</v>
+        <v>4.4707</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1703</v>
+        <v>3.5288</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8745</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>5.2977</v>
+        <v>5.3217</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0532</v>
+        <v>2.07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2445</v>
+        <v>3.2516</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6428</v>
+        <v>4.7794</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5614</v>
+        <v>1.6344</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0815</v>
+        <v>3.145</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6549</v>
+        <v>0.5423</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4919</v>
+        <v>0.4356</v>
       </c>
       <c r="O4" t="n">
-        <v>0.163</v>
+        <v>0.1067</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9079</v>
+        <v>0.2259</v>
       </c>
       <c r="T4" t="n">
-        <v>0.169</v>
+        <v>0.2409</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7388</v>
+        <v>-0.015</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1606</v>
+        <v>-0.1032</v>
       </c>
       <c r="W4" t="n">
-        <v>0.359</v>
+        <v>0.4558</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3059</v>
+        <v>4.0973</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2521</v>
+        <v>3.933</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0538</v>
+        <v>0.1642</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2155</v>
+        <v>1.5055</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0153</v>
+        <v>0.7128</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7999000000000001</v>
+        <v>0.7926</v>
       </c>
       <c r="J5" t="n">
-        <v>1.967</v>
+        <v>2.8949</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3232</v>
+        <v>1.5575</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6437</v>
+        <v>1.3374</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7515</v>
+        <v>-1.3894</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3079</v>
+        <v>-0.8447</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4436</v>
+        <v>-0.5447</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6002</v>
+        <v>1.5579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6007</v>
+        <v>1.5579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3688</v>
+        <v>1.0339</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5734</v>
+        <v>0.7587</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2046</v>
+        <v>0.2753</v>
       </c>
       <c r="V5" t="n">
-        <v>3.8591</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.8591</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0521</v>
+        <v>3.7609</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5016</v>
+        <v>0.9684</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5505</v>
+        <v>2.7926</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2251</v>
+        <v>1.7398</v>
       </c>
       <c r="H6" t="n">
-        <v>1.549</v>
+        <v>1.4316</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6761</v>
+        <v>0.3081</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4414</v>
+        <v>0.5133</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3214</v>
+        <v>1.129</v>
       </c>
       <c r="L6" t="n">
-        <v>0.12</v>
+        <v>-0.6156</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7837</v>
+        <v>1.2264</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2276</v>
+        <v>0.3027</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5561</v>
+        <v>0.9237</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0003</v>
+        <v>1.9474</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2271</v>
+        <v>0.1059</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4606</v>
+        <v>0.2077</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2335</v>
+        <v>-0.1018</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5999</v>
+        <v>0.9416</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5999</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4845</v>
+        <v>3.445</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7229</v>
+        <v>1.7575</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7616</v>
+        <v>1.6875</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7378</v>
+        <v>2.1862</v>
       </c>
       <c r="H7" t="n">
-        <v>1.456</v>
+        <v>1.5461</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2819</v>
+        <v>0.6401</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4255</v>
+        <v>1.5097</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0997</v>
+        <v>1.3881</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6742</v>
+        <v>0.1216</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3123</v>
+        <v>0.6765</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3563</v>
+        <v>0.158</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.5185</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0006</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1936</v>
+        <v>0.6484</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0979</v>
+        <v>0.611</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2915</v>
+        <v>0.0374</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6105</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>0.6105</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8009</v>
+        <v>2.7095</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8041</v>
+        <v>1.7653</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9968</v>
+        <v>0.9442</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3156</v>
+        <v>2.4288</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1691</v>
+        <v>1.7708</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4847</v>
+        <v>0.6579</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9268</v>
+        <v>4.1945</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4635</v>
+        <v>2.1681</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3903</v>
+        <v>2.0263</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6112</v>
+        <v>-1.7657</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7057</v>
+        <v>-0.3973</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0945</v>
+        <v>-1.3684</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>2.5316</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3166</v>
+        <v>0.9497</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3317</v>
+        <v>0.4919</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0151</v>
+        <v>0.4578</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1998</v>
+        <v>-0.2795</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3995</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2698</v>
+        <v>2.3902</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0557</v>
+        <v>1.3978</v>
       </c>
       <c r="F9" t="n">
-        <v>1.214</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4651</v>
+        <v>-0.3124</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7802</v>
+        <v>1.1561</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6849</v>
+        <v>-1.4685</v>
       </c>
       <c r="J9" t="n">
-        <v>4.0809</v>
+        <v>-0.7573</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0812</v>
+        <v>0.5389</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9997</v>
+        <v>-1.2962</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6158</v>
+        <v>0.4449</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.301</v>
+        <v>0.6172</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3149</v>
+        <v>-0.1723</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0009</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6007</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4646</v>
+        <v>0.8973</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0243</v>
+        <v>0.6867</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4889</v>
+        <v>0.2106</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2598</v>
+        <v>1.2211</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.4421</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2598</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,31 +1189,31 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8998</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6318</v>
+        <v>-0.5551</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7869</v>
+        <v>-0.7123</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1551</v>
+        <v>0.1572</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7867</v>
+        <v>-0.5069</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8067</v>
+        <v>-0.6269</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.658</v>
+        <v>-0.4043</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>0.3489</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.678</v>
+        <v>-0.7533</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1287</v>
+        <v>-0.1026</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.2289</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1287</v>
+        <v>0.1263</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2452</v>
+        <v>-0.3539</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1289</v>
+        <v>-0.2243</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1163</v>
+        <v>-0.1297</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9025</v>
+        <v>-0.6042</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0775</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.175</v>
+        <v>0.1635</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.536</v>
+        <v>-0.7834</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1538</v>
+        <v>0.0205</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6898</v>
+        <v>-0.804</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4924</v>
+        <v>-0.644</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3399</v>
+        <v>0.0205</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8323</v>
+        <v>-0.6645</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0437</v>
+        <v>-0.1395</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1861</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1425</v>
+        <v>-0.1395</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6002</v>
+        <v>0.3895</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.626</v>
+        <v>-0.2102</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4445</v>
+        <v>-0.1237</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1814</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8597</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8597</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.6633</v>
+        <v>-1.8651</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.0699</v>
+        <v>-2.2836</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4066</v>
+        <v>0.4186</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4551</v>
+        <v>-2.4997</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8328</v>
+        <v>-0.8739</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6222</v>
+        <v>-1.6258</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.7541</v>
+        <v>-1.7077</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.518</v>
+        <v>-0.5003</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.236</v>
+        <v>-1.2074</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.701</v>
+        <v>-0.792</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3148</v>
+        <v>-0.3736</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1488</v>
+        <v>-0.2543</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3156</v>
+        <v>0.3978</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.6521</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.822</v>
+        <v>-3.9885</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2884</v>
+        <v>-1.4865</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5336</v>
+        <v>-2.502</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.0158</v>
+        <v>-3.0069</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5985</v>
+        <v>-1.5527</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4173</v>
+        <v>-1.4542</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9725</v>
+        <v>-0.8728</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0125</v>
+        <v>-0.9133</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0433</v>
+        <v>-2.1342</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4573</v>
+        <v>-1.4947</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.2395</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3156</v>
+        <v>0.3599</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2908</v>
+        <v>-0.1204</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26.7332</v>
+        <v>27.06299999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>17.5931</v>
+        <v>20.0232</v>
       </c>
       <c r="F17" t="n">
-        <v>9.1402</v>
+        <v>7.040100000000002</v>
       </c>
       <c r="G17" t="n">
-        <v>10.744</v>
+        <v>10.8359</v>
       </c>
       <c r="H17" t="n">
-        <v>12.0656</v>
+        <v>12.1975</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3215</v>
+        <v>-1.3619</v>
       </c>
       <c r="J17" t="n">
-        <v>15.5827</v>
+        <v>16.92</v>
       </c>
       <c r="K17" t="n">
-        <v>12.4671</v>
+        <v>13.3348</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1157</v>
+        <v>3.585</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.838799999999999</v>
+        <v>-6.0843</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4013000000000001</v>
+        <v>-1.1374</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.437399999999999</v>
+        <v>-4.9468</v>
       </c>
       <c r="P17" t="n">
-        <v>5.0015</v>
+        <v>4.8684</v>
       </c>
       <c r="Q17" t="n">
-        <v>-13.0039</v>
+        <v>-12.658</v>
       </c>
       <c r="R17" t="n">
-        <v>18.0052</v>
+        <v>17.5265</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2899</v>
+        <v>4.467</v>
       </c>
       <c r="T17" t="n">
-        <v>3.757900000000001</v>
+        <v>4.1394</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5320999999999996</v>
+        <v>0.3276000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>6.697999999999999</v>
+        <v>6.891999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>11.2562</v>
+        <v>11.6216</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.5583</v>
+        <v>-4.7297</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1393</v>
+        <v>4.5656</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6389</v>
+        <v>5.0408</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4997</v>
+        <v>-0.4753</v>
       </c>
       <c r="G18" t="n">
-        <v>4.1232</v>
+        <v>4.2236</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1756</v>
+        <v>0.174</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9476</v>
+        <v>4.0497</v>
       </c>
       <c r="J18" t="n">
-        <v>6.5319</v>
+        <v>6.8274</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4829</v>
+        <v>2.6121</v>
       </c>
       <c r="L18" t="n">
-        <v>4.0489</v>
+        <v>4.2154</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4086</v>
+        <v>-2.6038</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3073</v>
+        <v>-2.4381</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1013</v>
+        <v>-0.1657</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4708</v>
+        <v>-0.2543</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.211</v>
+        <v>-0.2824</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2598</v>
+        <v>0.0281</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4874</v>
+        <v>2.5436</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1682</v>
+        <v>0.1531</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1621</v>
+        <v>1.6405</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2743</v>
+        <v>2.7096</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1122</v>
+        <v>-1.0691</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6761</v>
+        <v>1.6369</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3876</v>
+        <v>0.3222</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2886</v>
+        <v>1.3147</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9635</v>
+        <v>2.0368</v>
       </c>
       <c r="K19" t="n">
-        <v>0.16</v>
+        <v>0.1642</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8036</v>
+        <v>1.8726</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2874</v>
+        <v>-0.3999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2276</v>
+        <v>0.158</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.515</v>
+        <v>-0.5578</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5422</v>
+        <v>-0.0132</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1113</v>
+        <v>0.4255</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6534</v>
+        <v>-0.4386</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1719</v>
+        <v>-0.178</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2855</v>
+        <v>0.4264</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0245</v>
+        <v>0.0784</v>
       </c>
       <c r="F20" t="n">
-        <v>0.31</v>
+        <v>0.348</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1113</v>
+        <v>0.1011</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3112</v>
+        <v>0.3063</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0258</v>
+        <v>0.1306</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0645</v>
+        <v>0.0378</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0387</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2855</v>
+        <v>0.4264</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0245</v>
+        <v>0.0784</v>
       </c>
       <c r="F21" t="n">
-        <v>0.31</v>
+        <v>0.348</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1113</v>
+        <v>0.1011</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3112</v>
+        <v>0.3063</v>
       </c>
       <c r="J21" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0258</v>
+        <v>0.1306</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0645</v>
+        <v>0.0378</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0387</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2012</v>
+        <v>-0.0786</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5461</v>
+        <v>0.7285</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.345</v>
+        <v>-0.8071</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5253</v>
+        <v>-0.627</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3614</v>
+        <v>-1.4292</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8361</v>
+        <v>0.8022</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3617</v>
+        <v>0.3992</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0818</v>
+        <v>0.1155</v>
       </c>
       <c r="L22" t="n">
-        <v>0.28</v>
+        <v>0.2837</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8871</v>
+        <v>-1.0262</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4432</v>
+        <v>-1.5447</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5561</v>
+        <v>0.5185</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0069</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0499</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1528</v>
+        <v>-0.0429</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9513</v>
+        <v>-1.0164</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2111</v>
+        <v>-1.2959</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4433</v>
+        <v>-0.3078</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1534</v>
+        <v>-0.0453</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2899</v>
+        <v>-0.2625</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.353</v>
+        <v>-0.3766</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0469</v>
+        <v>0.034</v>
       </c>
       <c r="J23" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.393</v>
+        <v>-0.4171</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0069</v>
+        <v>-0.0066</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2903</v>
+        <v>-0.126</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1934</v>
+        <v>-0.0858</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0969</v>
+        <v>-0.0401</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8875</v>
+        <v>-2.077</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8373</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7249</v>
+        <v>-2.8961</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4153</v>
+        <v>0.444</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9946</v>
+        <v>1.0715</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5793</v>
+        <v>-0.6276</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1666</v>
+        <v>2.3478</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9667</v>
+        <v>2.1451</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2</v>
+        <v>0.2026</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7514</v>
+        <v>-1.9038</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9721</v>
+        <v>-1.0736</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9497</v>
+        <v>0.6823</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1519</v>
+        <v>0.8334</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2022</v>
+        <v>-0.1511</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.452</v>
+        <v>-1.4506</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.9716</v>
+        <v>-2.0096</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5234</v>
+        <v>-2.8118</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6759</v>
+        <v>-1.6446</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8475</v>
+        <v>-1.1672</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.2804</v>
+        <v>-1.2545</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7693</v>
+        <v>-0.7456</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5112</v>
+        <v>-0.509</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5491</v>
+        <v>0.7033</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5453</v>
+        <v>0.6544</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8295</v>
+        <v>-1.9578</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3145</v>
+        <v>-1.4</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.515</v>
+        <v>-0.5578</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7231</v>
+        <v>-1.0247</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2244</v>
+        <v>-0.4005</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4987</v>
+        <v>-0.6241</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="26">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.9601</v>
+        <v>-3.8552</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5386</v>
+        <v>-1.2564</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4215</v>
+        <v>-2.5988</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.8659</v>
+        <v>-1.9268</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8154</v>
+        <v>-0.8308</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0418</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0418</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.9077</v>
+        <v>-2.0013</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8572</v>
+        <v>-0.9052</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5746</v>
+        <v>-0.3694</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.3572</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0055</v>
+        <v>-0.0122</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.165</v>
+        <v>-6.783</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.5935</v>
+        <v>-3.808</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.5715</v>
+        <v>-2.975</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.2039</v>
+        <v>-3.9745</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.6953</v>
+        <v>-1.655</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4915</v>
+        <v>-2.3195</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6253</v>
+        <v>-1.7443</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.5208</v>
       </c>
       <c r="L27" t="n">
-        <v>2.5996</v>
+        <v>-1.2235</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.8292</v>
+        <v>-2.2302</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.721</v>
+        <v>-1.1342</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1082</v>
+        <v>-1.096</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.6007</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.0011</v>
+        <v>-1.9474</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4004</v>
+        <v>1.1684</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.361</v>
+        <v>-0.8085</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2177</v>
+        <v>-0.1163</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1432</v>
+        <v>-0.6922</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.9994</v>
+        <v>-1.2211</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.9994</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-7.8607</v>
+        <v>-7.4078</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.5661</v>
+        <v>-2.6571</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.2946</v>
+        <v>-4.7507</v>
       </c>
       <c r="G28" t="n">
-        <v>-3.906</v>
+        <v>-1.2555</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.5814</v>
+        <v>-3.7306</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.3246</v>
+        <v>2.4751</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.8121</v>
+        <v>1.7286</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.538</v>
+        <v>-0.9056</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.2741</v>
+        <v>2.6342</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.0938</v>
+        <v>-2.9841</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.0433</v>
+        <v>-2.825</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.0505</v>
+        <v>-0.1591</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.8002</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q28" t="n">
-        <v>-2.0006</v>
+        <v>-3.8947</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.9547</v>
+        <v>-0.5681</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7534</v>
+        <v>-0.491</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.2013</v>
+        <v>-0.0771</v>
       </c>
       <c r="V28" t="n">
-        <v>-1.1998</v>
+        <v>-3.0526</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.1998</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="29">
@@ -2671,67 +2671,67 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-9.966900000000001</v>
+        <v>-9.162699999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.8605</v>
+        <v>-7.0835</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.1064</v>
+        <v>-2.0792</v>
       </c>
       <c r="G29" t="n">
-        <v>-8.0465</v>
+        <v>-7.9275</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.6009</v>
+        <v>-4.5531</v>
       </c>
       <c r="I29" t="n">
-        <v>-3.4456</v>
+        <v>-3.3744</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.7089</v>
+        <v>-6.4105</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.3646</v>
+        <v>-3.2018</v>
       </c>
       <c r="L29" t="n">
-        <v>-3.3443</v>
+        <v>-3.2087</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.3377</v>
+        <v>-1.5169</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.2363</v>
+        <v>-1.3512</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.1013</v>
+        <v>-0.1657</v>
       </c>
       <c r="P29" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R29" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.3488</v>
+        <v>-0.6151</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.4111</v>
+        <v>0.0212</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.9378</v>
+        <v>-0.6364</v>
       </c>
       <c r="V29" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
       <c r="W29" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X29" t="n">
-        <v>-1.6315</v>
+        <v>-1.6785</v>
       </c>
     </row>
     <row r="30">
@@ -2749,67 +2749,67 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-26.7333</v>
+        <v>-25.425</v>
       </c>
       <c r="E30" t="n">
-        <v>-9.1404</v>
+        <v>-7.0401</v>
       </c>
       <c r="F30" t="n">
-        <v>-17.5932</v>
+        <v>-18.385</v>
       </c>
       <c r="G30" t="n">
-        <v>-10.7438</v>
+        <v>-10.8357</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.0656</v>
+        <v>-12.1977</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3219</v>
+        <v>1.3618</v>
       </c>
       <c r="J30" t="n">
-        <v>4.838899999999999</v>
+        <v>6.084200000000002</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4015999999999997</v>
+        <v>1.1375</v>
       </c>
       <c r="L30" t="n">
-        <v>4.437500000000002</v>
+        <v>4.9467</v>
       </c>
       <c r="M30" t="n">
-        <v>-15.5828</v>
+        <v>-16.9201</v>
       </c>
       <c r="N30" t="n">
-        <v>-12.467</v>
+        <v>-13.3351</v>
       </c>
       <c r="O30" t="n">
-        <v>-3.1157</v>
+        <v>-3.5848</v>
       </c>
       <c r="P30" t="n">
-        <v>-5.0012</v>
+        <v>-4.868600000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>-18.0052</v>
+        <v>-17.5263</v>
       </c>
       <c r="R30" t="n">
-        <v>13.0038</v>
+        <v>12.6578</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.2901</v>
+        <v>-2.8289</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.5322999999999998</v>
+        <v>-0.3276</v>
       </c>
       <c r="U30" t="n">
-        <v>-3.7576</v>
+        <v>-2.501</v>
       </c>
       <c r="V30" t="n">
-        <v>-6.6979</v>
+        <v>-6.8921</v>
       </c>
       <c r="W30" t="n">
-        <v>4.5582</v>
+        <v>4.7296</v>
       </c>
       <c r="X30" t="n">
-        <v>-11.2561</v>
+        <v>-11.6216</v>
       </c>
     </row>
   </sheetData>
